--- a/Deliverables/BOM/Electrode-Board/PCBWay_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/PCBWay_BOM_Electrode_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E016B142-1866-48D9-81BD-991AF18CAE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52EDEA9-CCC1-4CDE-8CE4-C9CEE762572C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,9 +80,6 @@
     <t>D1, D2</t>
   </si>
   <si>
-    <t>J1</t>
-  </si>
-  <si>
     <t>P1</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
     <t>100V -55℃~+150℃@(Tj) 400mW Single 1.25V@150mA 4ns 1μA@75V 200mA SOD-323 Switching Diode ROHS</t>
   </si>
   <si>
-    <t>CONN FFC BOTTOM 6POS 0.50MM R/A</t>
-  </si>
-  <si>
     <t>Sensor Connecting Pads</t>
   </si>
   <si>
@@ -164,9 +158,6 @@
     <t>SOD-323</t>
   </si>
   <si>
-    <t>FH19C-6S-0.5SH(10)</t>
-  </si>
-  <si>
     <t>sEMG sensor</t>
   </si>
   <si>
@@ -219,9 +210,6 @@
   </si>
   <si>
     <t>Yageo</t>
-  </si>
-  <si>
-    <t>Hirose</t>
   </si>
   <si>
     <t>FH</t>
@@ -279,9 +267,6 @@
 </t>
   </si>
   <si>
-    <t>C424651</t>
-  </si>
-  <si>
     <t>-------</t>
   </si>
   <si>
@@ -321,9 +306,6 @@
     <t xml:space="preserve">Shikues </t>
   </si>
   <si>
-    <t>Quantity (Per Board)</t>
-  </si>
-  <si>
     <t>10uF</t>
   </si>
   <si>
@@ -331,6 +313,24 @@
   </si>
   <si>
     <t>RC-02W8062FT</t>
+  </si>
+  <si>
+    <t>P9</t>
+  </si>
+  <si>
+    <t>Ribbon wire Connection Pads</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>6 pin Ribbon Pads.</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT</t>
+  </si>
+  <si>
+    <t>Quantity (1 Board)</t>
   </si>
 </sst>
 </file>
@@ -340,7 +340,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,6 +467,30 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -504,7 +528,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -742,11 +766,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -886,9 +921,6 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -900,6 +932,39 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1274,10 +1339,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1313,7 +1378,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="60"/>
+      <c r="L3" s="70"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1331,7 +1396,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="61"/>
+      <c r="L4" s="71"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1349,7 +1414,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="61"/>
+      <c r="L5" s="71"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1363,7 +1428,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="61"/>
+      <c r="L6" s="71"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1377,7 +1442,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="61"/>
+      <c r="L7" s="71"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1391,7 +1456,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="61"/>
+      <c r="L8" s="71"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1402,31 +1467,31 @@
         <v>10</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" s="57" t="s">
-        <v>96</v>
+        <v>64</v>
+      </c>
+      <c r="J9" s="56" t="s">
+        <v>99</v>
       </c>
       <c r="K9" s="52" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1439,22 +1504,22 @@
         <v>11</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J10" s="37">
         <v>1</v>
@@ -1474,22 +1539,22 @@
         <v>12</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="55" t="s">
-        <v>93</v>
+        <v>40</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>88</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J11" s="39">
         <v>1</v>
@@ -1502,29 +1567,29 @@
     <row r="12" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="31">
-        <f>ROW(B12) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="37" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J12" s="37">
         <v>1</v>
@@ -1544,27 +1609,27 @@
         <v>14</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F13" s="40" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J13" s="39">
         <v>1</v>
       </c>
-      <c r="K13" s="58">
+      <c r="K13" s="57">
         <v>50</v>
       </c>
       <c r="L13" s="39"/>
@@ -1572,29 +1637,29 @@
     <row r="14" spans="1:12" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="31">
-        <f>ROW(B14) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="37" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I14" s="53" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J14" s="37">
         <v>2</v>
@@ -1610,70 +1675,72 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="H15" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="I15" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="J15" s="39">
+      <c r="D15" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="64">
         <v>1</v>
       </c>
-      <c r="K15" s="39">
-        <v>42</v>
-      </c>
-      <c r="L15" s="39"/>
+      <c r="K15" s="67">
+        <v>40</v>
+      </c>
+      <c r="L15" s="68" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="31">
-        <f>ROW(B16) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="H16" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="I16" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="J16" s="37">
+      <c r="C16" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16" s="58">
         <v>1</v>
       </c>
-      <c r="K16" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="L16" s="53" t="s">
-        <v>83</v>
+      <c r="K16" s="63">
+        <v>40</v>
+      </c>
+      <c r="L16" s="61" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1683,25 +1750,25 @@
         <v>8</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F17" s="40" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H17" s="40" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J17" s="39">
         <v>1</v>
@@ -1714,29 +1781,29 @@
     <row r="18" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="31">
-        <f>ROW(B18) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J18" s="37">
         <v>5</v>
@@ -1753,25 +1820,25 @@
         <v>10</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F19" s="40" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H19" s="40" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J19" s="39">
         <v>2</v>
@@ -1784,29 +1851,29 @@
     <row r="20" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="31">
-        <f>ROW(B20) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I20" s="53" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J20" s="37">
         <v>1</v>
@@ -1823,25 +1890,25 @@
         <v>12</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F21" s="40" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H21" s="40" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J21" s="39">
         <v>1</v>
@@ -1854,29 +1921,29 @@
     <row r="22" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="31">
-        <f>ROW(B22) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H22" s="51" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I22" s="53" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J22" s="37">
         <v>1</v>
@@ -1893,25 +1960,25 @@
         <v>14</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F23" s="40" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H23" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="I23" s="56" t="s">
-        <v>91</v>
+        <v>85</v>
+      </c>
+      <c r="I23" s="55" t="s">
+        <v>86</v>
       </c>
       <c r="J23" s="39">
         <v>1</v>

--- a/Deliverables/BOM/Electrode-Board/PCBWay_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/PCBWay_BOM_Electrode_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52EDEA9-CCC1-4CDE-8CE4-C9CEE762572C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3AEE223-8BA0-41F6-A488-9BB766C3D292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="106">
   <si>
     <t>Component list</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>R7, R8</t>
-  </si>
-  <si>
-    <t>R9</t>
   </si>
   <si>
     <t>R10</t>
@@ -331,6 +328,27 @@
   </si>
   <si>
     <t>Quantity (1 Board)</t>
+  </si>
+  <si>
+    <t>Item Type</t>
+  </si>
+  <si>
+    <t>Capacitor</t>
+  </si>
+  <si>
+    <t>Diode</t>
+  </si>
+  <si>
+    <t>SMD Pads</t>
+  </si>
+  <si>
+    <t>Resistor</t>
+  </si>
+  <si>
+    <t>Ics</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -528,7 +546,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -777,11 +795,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -974,6 +1018,41 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1002,13 +1081,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1316,701 +1395,738 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" customWidth="1"/>
-    <col min="9" max="9" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" customWidth="1"/>
+    <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
-      <c r="C1" s="2"/>
+      <c r="C1" s="19"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="69"/>
+      <c r="I1" s="2"/>
       <c r="J1" s="69"/>
       <c r="K1" s="69"/>
       <c r="L1" s="69"/>
-    </row>
-    <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M1" s="69"/>
+    </row>
+    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="72"/>
+      <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="3"/>
+      <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="42"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L2" s="3"/>
+      <c r="M2" s="42"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="73"/>
+      <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="4"/>
+      <c r="G3" s="12"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="70"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L3" s="4"/>
+      <c r="M3" s="70"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="73"/>
+      <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="47" t="s">
+      <c r="E4" s="12"/>
+      <c r="F4" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="6"/>
+      <c r="G4" s="13"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="71"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="6"/>
+      <c r="M4" s="71"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="73"/>
+      <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="48" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="5"/>
+      <c r="G5" s="14"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="71"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L5" s="5"/>
+      <c r="M5" s="71"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="74"/>
       <c r="D6" s="15"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="5"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="14"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="71"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="5"/>
+      <c r="M6" s="71"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="17"/>
+      <c r="C7" s="75"/>
       <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="7"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="17"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="71"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="7"/>
+      <c r="M7" s="71"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
+      <c r="C8" s="76"/>
       <c r="D8" s="27"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="7"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="17"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="71"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="7"/>
+      <c r="M8" s="71"/>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="52" t="s">
-        <v>72</v>
-      </c>
-      <c r="I9" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="J9" s="56" t="s">
-        <v>99</v>
-      </c>
-      <c r="K9" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E9" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="L9" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="M9" s="29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="31">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="79" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="J10" s="37">
+      <c r="E10" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="K10" s="37">
         <v>1</v>
       </c>
-      <c r="K10" s="37">
+      <c r="L10" s="37">
         <v>60</v>
       </c>
-      <c r="L10" s="37"/>
-    </row>
-    <row r="11" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="37"/>
+    </row>
+    <row r="11" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="31">
         <f t="shared" ref="B11:B23" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="80"/>
+      <c r="D11" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="I11" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="39">
+      <c r="E11" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="K11" s="39">
         <v>1</v>
       </c>
-      <c r="K11" s="39">
+      <c r="L11" s="39">
         <v>50</v>
       </c>
-      <c r="L11" s="39"/>
-    </row>
-    <row r="12" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="39"/>
+    </row>
+    <row r="12" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="31">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="80"/>
+      <c r="D12" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" s="37">
+      <c r="E12" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="37">
         <v>1</v>
       </c>
-      <c r="K12" s="37">
+      <c r="L12" s="37">
         <v>100</v>
       </c>
-      <c r="L12" s="37"/>
-    </row>
-    <row r="13" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="37"/>
+    </row>
+    <row r="13" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="31">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="80"/>
+      <c r="D13" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="J13" s="39">
+      <c r="E13" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="K13" s="39">
         <v>1</v>
       </c>
-      <c r="K13" s="57">
+      <c r="L13" s="57">
         <v>50</v>
       </c>
-      <c r="L13" s="39"/>
-    </row>
-    <row r="14" spans="1:12" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="39"/>
+    </row>
+    <row r="14" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="31">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="I14" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="37">
+      <c r="E14" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="37">
         <v>2</v>
       </c>
-      <c r="K14" s="37">
+      <c r="L14" s="37">
         <v>100</v>
       </c>
-      <c r="L14" s="37"/>
-    </row>
-    <row r="15" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M14" s="37"/>
+    </row>
+    <row r="15" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="31">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="66" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="67" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" s="66" t="s">
-        <v>78</v>
-      </c>
-      <c r="I15" s="67" t="s">
-        <v>86</v>
-      </c>
-      <c r="J15" s="64">
+      <c r="E15" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" s="64">
         <v>1</v>
       </c>
-      <c r="K15" s="67">
+      <c r="L15" s="67">
         <v>40</v>
       </c>
-      <c r="L15" s="68" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="68" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="31">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="82"/>
+      <c r="D16" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="59" t="s">
+      <c r="F16" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="60" t="s">
+      <c r="G16" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="H16" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="K16" s="58">
+        <v>1</v>
+      </c>
+      <c r="L16" s="63">
+        <v>40</v>
+      </c>
+      <c r="M16" s="61" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="H16" s="62" t="s">
-        <v>78</v>
-      </c>
-      <c r="I16" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="J16" s="58">
-        <v>1</v>
-      </c>
-      <c r="K16" s="63">
-        <v>40</v>
-      </c>
-      <c r="L16" s="61" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="31">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="79" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="H17" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="J17" s="39">
+      <c r="E17" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" s="39">
         <v>1</v>
       </c>
-      <c r="K17" s="39">
+      <c r="L17" s="39">
         <v>100</v>
       </c>
-      <c r="L17" s="39"/>
-    </row>
-    <row r="18" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="39"/>
+    </row>
+    <row r="18" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="31">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="80"/>
+      <c r="D18" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="J18" s="37">
+      <c r="E18" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="K18" s="37">
         <v>5</v>
       </c>
-      <c r="K18" s="37">
+      <c r="L18" s="37">
         <v>300</v>
       </c>
-      <c r="L18" s="37"/>
-    </row>
-    <row r="19" spans="1:12" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M18" s="37"/>
+    </row>
+    <row r="19" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="31">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="80"/>
+      <c r="D19" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="H19" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="I19" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="J19" s="39">
+      <c r="E19" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19" s="39">
         <v>2</v>
       </c>
-      <c r="K19" s="39">
+      <c r="L19" s="39">
         <v>100</v>
       </c>
-      <c r="L19" s="39"/>
-    </row>
-    <row r="20" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M19" s="39"/>
+    </row>
+    <row r="20" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="31">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="J20" s="37">
+      <c r="C20" s="80"/>
+      <c r="D20" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="J20" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="K20" s="37">
         <v>1</v>
       </c>
-      <c r="K20" s="37">
+      <c r="L20" s="37">
         <v>45</v>
       </c>
-      <c r="L20" s="37"/>
-    </row>
-    <row r="21" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M20" s="37"/>
+    </row>
+    <row r="21" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="31">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="J21" s="39">
+      <c r="C21" s="82"/>
+      <c r="D21" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="J21" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="39">
         <v>1</v>
       </c>
-      <c r="K21" s="39">
+      <c r="L21" s="39">
         <v>100</v>
       </c>
-      <c r="L21" s="39"/>
-    </row>
-    <row r="22" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M21" s="39"/>
+    </row>
+    <row r="22" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="31">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="I22" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="J22" s="37">
+      <c r="C22" s="79" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="J22" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="K22" s="37">
         <v>1</v>
       </c>
-      <c r="K22" s="37">
+      <c r="L22" s="37">
         <v>42</v>
       </c>
-      <c r="L22" s="37"/>
-    </row>
-    <row r="23" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M22" s="37"/>
+    </row>
+    <row r="23" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="31">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="H23" s="40" t="s">
+      <c r="C23" s="82"/>
+      <c r="D23" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="I23" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="J23" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="I23" s="55" t="s">
-        <v>86</v>
-      </c>
-      <c r="J23" s="39">
+      <c r="K23" s="39">
         <v>1</v>
       </c>
-      <c r="K23" s="39">
+      <c r="L23" s="39">
         <v>42</v>
       </c>
-      <c r="L23" s="41"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M23" s="41"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="32"/>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="77"/>
+      <c r="D24" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="34"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="35"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="36"/>
       <c r="H24" s="35"/>
-      <c r="I24" s="36"/>
+      <c r="I24" s="35"/>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
-      <c r="L24" s="43"/>
-    </row>
-    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L24" s="36"/>
+      <c r="M24" s="43"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="24"/>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="78"/>
+      <c r="D25" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
@@ -2018,12 +2134,17 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="44"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="L3:L8"/>
+  <mergeCells count="6">
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="M3:M8"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Deliverables/BOM/Electrode-Board/PCBWay_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/PCBWay_BOM_Electrode_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3AEE223-8BA0-41F6-A488-9BB766C3D292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42797424-FD86-422D-AFB5-8E5FB0D3AE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1010,15 +1010,6 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1042,16 +1033,25 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1420,15 +1420,15 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
     </row>
     <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
-      <c r="C2" s="72"/>
+      <c r="C2" s="69"/>
       <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
@@ -1447,7 +1447,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="73"/>
+      <c r="C3" s="70"/>
       <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
@@ -1461,12 +1461,12 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
-      <c r="M3" s="70"/>
+      <c r="M3" s="80"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="73"/>
+      <c r="C4" s="70"/>
       <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
@@ -1480,12 +1480,12 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="71"/>
+      <c r="M4" s="81"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="73"/>
+      <c r="C5" s="70"/>
       <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
@@ -1499,12 +1499,12 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="71"/>
+      <c r="M5" s="81"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
-      <c r="C6" s="74"/>
+      <c r="C6" s="71"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
@@ -1514,12 +1514,12 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="71"/>
+      <c r="M6" s="81"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="75"/>
+      <c r="C7" s="72"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
@@ -1529,12 +1529,12 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="71"/>
+      <c r="M7" s="81"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="76"/>
+      <c r="C8" s="73"/>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
@@ -1544,7 +1544,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="71"/>
+      <c r="M8" s="81"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1591,7 +1591,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="77" t="s">
         <v>100</v>
       </c>
       <c r="D10" s="37" t="s">
@@ -1629,7 +1629,7 @@
         <f t="shared" ref="B11:B23" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="80"/>
+      <c r="C11" s="82"/>
       <c r="D11" s="39" t="s">
         <v>12</v>
       </c>
@@ -1665,7 +1665,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="80"/>
+      <c r="C12" s="82"/>
       <c r="D12" s="37" t="s">
         <v>13</v>
       </c>
@@ -1701,7 +1701,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="80"/>
+      <c r="C13" s="82"/>
       <c r="D13" s="39" t="s">
         <v>14</v>
       </c>
@@ -1737,7 +1737,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="81" t="s">
+      <c r="C14" s="76" t="s">
         <v>101</v>
       </c>
       <c r="D14" s="37" t="s">
@@ -1775,7 +1775,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="79" t="s">
+      <c r="C15" s="77" t="s">
         <v>102</v>
       </c>
       <c r="D15" s="64" t="s">
@@ -1815,7 +1815,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="82"/>
+      <c r="C16" s="78"/>
       <c r="D16" s="58" t="s">
         <v>93</v>
       </c>
@@ -1853,7 +1853,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="77" t="s">
         <v>103</v>
       </c>
       <c r="D17" s="39" t="s">
@@ -1891,7 +1891,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="80"/>
+      <c r="C18" s="82"/>
       <c r="D18" s="37" t="s">
         <v>18</v>
       </c>
@@ -1927,7 +1927,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="80"/>
+      <c r="C19" s="82"/>
       <c r="D19" s="39" t="s">
         <v>19</v>
       </c>
@@ -1963,7 +1963,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="80"/>
+      <c r="C20" s="82"/>
       <c r="D20" s="37" t="s">
         <v>105</v>
       </c>
@@ -1999,7 +1999,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="82"/>
+      <c r="C21" s="78"/>
       <c r="D21" s="39" t="s">
         <v>20</v>
       </c>
@@ -2035,7 +2035,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="77" t="s">
         <v>104</v>
       </c>
       <c r="D22" s="37" t="s">
@@ -2073,7 +2073,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="82"/>
+      <c r="C23" s="78"/>
       <c r="D23" s="39" t="s">
         <v>22</v>
       </c>
@@ -2106,7 +2106,7 @@
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="32"/>
-      <c r="C24" s="77"/>
+      <c r="C24" s="74"/>
       <c r="D24" s="33" t="s">
         <v>5</v>
       </c>
@@ -2123,7 +2123,7 @@
     <row r="25" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="24"/>
-      <c r="C25" s="78"/>
+      <c r="C25" s="75"/>
       <c r="D25" s="8" t="s">
         <v>6</v>
       </c>

--- a/Deliverables/BOM/Electrode-Board/PCBWay_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/PCBWay_BOM_Electrode_Board.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25501"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42797424-FD86-422D-AFB5-8E5FB0D3AE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BA5C27-1541-407F-993C-EEDC5D2BC072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -173,9 +173,6 @@
     <t>Manufacturer Part Number</t>
   </si>
   <si>
-    <t>CL10A106MA8NRNC</t>
-  </si>
-  <si>
     <t>CC0402KRX5R7BB105</t>
   </si>
   <si>
@@ -246,9 +243,6 @@
   </si>
   <si>
     <t>LCSC/Part No</t>
-  </si>
-  <si>
-    <t>C2922482</t>
   </si>
   <si>
     <t>C307331</t>
@@ -349,6 +343,12 @@
   </si>
   <si>
     <t>s</t>
+  </si>
+  <si>
+    <t>C91606</t>
+  </si>
+  <si>
+    <t>GRM188R61E106MA73D</t>
   </si>
 </sst>
 </file>
@@ -827,20 +827,20 @@
   </cellStyleXfs>
   <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -850,18 +850,18 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -876,7 +876,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -886,8 +886,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -899,22 +899,22 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -933,15 +933,15 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1013,23 +1013,23 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1396,21 +1396,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
-    <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="29.42578125" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+    <col min="10" max="10" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1425,7 +1425,7 @@
       <c r="L1" s="79"/>
       <c r="M1" s="79"/>
     </row>
-    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="69"/>
@@ -1444,7 +1444,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="42"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="70"/>
@@ -1463,7 +1463,7 @@
       <c r="L3" s="4"/>
       <c r="M3" s="80"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="70"/>
@@ -1482,7 +1482,7 @@
       <c r="L4" s="6"/>
       <c r="M4" s="81"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="70"/>
@@ -1501,7 +1501,7 @@
       <c r="L5" s="5"/>
       <c r="M5" s="81"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="71"/>
@@ -1516,7 +1516,7 @@
       <c r="L6" s="5"/>
       <c r="M6" s="81"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="72"/>
@@ -1531,7 +1531,7 @@
       <c r="L7" s="7"/>
       <c r="M7" s="81"/>
     </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="73"/>
@@ -1546,13 +1546,13 @@
       <c r="L8" s="7"/>
       <c r="M8" s="81"/>
     </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>10</v>
@@ -1567,32 +1567,32 @@
         <v>46</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I9" s="52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K9" s="56" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L9" s="52" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M9" s="29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="31">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="77" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>11</v>
@@ -1603,27 +1603,27 @@
       <c r="F10" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="38" t="s">
-        <v>47</v>
+      <c r="G10" s="51" t="s">
+        <v>105</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I10" s="49" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K10" s="37">
         <v>1</v>
       </c>
       <c r="L10" s="37">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M10" s="37"/>
     </row>
-    <row r="11" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="31">
         <f t="shared" ref="B11:B23" si="0">ROW(B11) - ROW($B$9)</f>
@@ -1640,16 +1640,16 @@
         <v>39</v>
       </c>
       <c r="G11" s="54" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J11" s="39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K11" s="39">
         <v>1</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="M11" s="39"/>
     </row>
-    <row r="12" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="31">
         <f t="shared" si="0"/>
@@ -1676,16 +1676,16 @@
         <v>39</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K12" s="37">
         <v>1</v>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="M12" s="37"/>
     </row>
-    <row r="13" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="31">
         <f t="shared" si="0"/>
@@ -1712,16 +1712,16 @@
         <v>39</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K13" s="39">
         <v>1</v>
@@ -1731,14 +1731,14 @@
       </c>
       <c r="M13" s="39"/>
     </row>
-    <row r="14" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="31">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D14" s="37" t="s">
         <v>15</v>
@@ -1750,16 +1750,16 @@
         <v>40</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K14" s="37">
         <v>2</v>
@@ -1769,14 +1769,14 @@
       </c>
       <c r="M14" s="37"/>
     </row>
-    <row r="15" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="31">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="77" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D15" s="64" t="s">
         <v>16</v>
@@ -1788,16 +1788,16 @@
         <v>41</v>
       </c>
       <c r="G15" s="66" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H15" s="67" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I15" s="66" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J15" s="67" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K15" s="64">
         <v>1</v>
@@ -1806,10 +1806,10 @@
         <v>40</v>
       </c>
       <c r="M15" s="68" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="31">
         <f t="shared" si="0"/>
@@ -1817,25 +1817,25 @@
       </c>
       <c r="C16" s="78"/>
       <c r="D16" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="G16" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="F16" s="60" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" s="58" t="s">
-        <v>96</v>
-      </c>
       <c r="H16" s="63" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I16" s="62" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J16" s="63" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K16" s="58">
         <v>1</v>
@@ -1844,17 +1844,17 @@
         <v>40</v>
       </c>
       <c r="M16" s="61" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="31">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="77" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>17</v>
@@ -1866,16 +1866,16 @@
         <v>42</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I17" s="40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K17" s="39">
         <v>1</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="M17" s="39"/>
     </row>
-    <row r="18" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="31">
         <f t="shared" si="0"/>
@@ -1902,16 +1902,16 @@
         <v>42</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I18" s="38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K18" s="37">
         <v>5</v>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="M18" s="37"/>
     </row>
-    <row r="19" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="31">
         <f t="shared" si="0"/>
@@ -1938,16 +1938,16 @@
         <v>42</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I19" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J19" s="39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K19" s="39">
         <v>2</v>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="M19" s="39"/>
     </row>
-    <row r="20" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="31">
         <f t="shared" si="0"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C20" s="82"/>
       <c r="D20" s="37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E20" s="38" t="s">
         <v>33</v>
@@ -1977,13 +1977,13 @@
         <v>43</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J20" s="53" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K20" s="37">
         <v>1</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="M20" s="37"/>
     </row>
-    <row r="21" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="31">
         <f t="shared" si="0"/>
@@ -2010,16 +2010,16 @@
         <v>42</v>
       </c>
       <c r="G21" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I21" s="40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J21" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K21" s="39">
         <v>1</v>
@@ -2029,14 +2029,14 @@
       </c>
       <c r="M21" s="39"/>
     </row>
-    <row r="22" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="31">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="77" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D22" s="37" t="s">
         <v>21</v>
@@ -2048,16 +2048,16 @@
         <v>44</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I22" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="J22" s="53" t="s">
         <v>83</v>
-      </c>
-      <c r="J22" s="53" t="s">
-        <v>85</v>
       </c>
       <c r="K22" s="37">
         <v>1</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="M22" s="37"/>
     </row>
-    <row r="23" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="31">
         <f t="shared" si="0"/>
@@ -2084,16 +2084,16 @@
         <v>45</v>
       </c>
       <c r="G23" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I23" s="40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J23" s="55" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K23" s="39">
         <v>1</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="M23" s="41"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="32"/>
       <c r="C24" s="74"/>
@@ -2120,7 +2120,7 @@
       <c r="L24" s="36"/>
       <c r="M24" s="43"/>
     </row>
-    <row r="25" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="24"/>
       <c r="C25" s="75"/>
